--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="КОМЕРС НОВИ ПАЗАР ЕООД" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -70,28 +73,94 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1186 Севлиево</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1119 Асеновград</t>
+  </si>
+  <si>
+    <t>1163 София Ботевградско шосе</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1167 В. Търново вход</t>
+  </si>
+  <si>
     <t>78970110027720134</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2Л EKO ЛЯTHA TEЧHOCT</t>
-  </si>
-  <si>
-    <t>21:58</t>
-  </si>
-  <si>
-    <t>17:07</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>17:19</t>
-  </si>
-  <si>
-    <t>19:55</t>
+    <t>2L SUMMER SCREEN WASH LIQUID</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>21:58:00</t>
+  </si>
+  <si>
+    <t>17:08:00</t>
+  </si>
+  <si>
+    <t>16:08:00</t>
+  </si>
+  <si>
+    <t>17:19:00</t>
+  </si>
+  <si>
+    <t>19:56:00</t>
+  </si>
+  <si>
+    <t>08:10:00</t>
+  </si>
+  <si>
+    <t>16:53:00</t>
+  </si>
+  <si>
+    <t>23:13:00</t>
+  </si>
+  <si>
+    <t>3231385127 3231385127</t>
+  </si>
+  <si>
+    <t>3231456854 3231456854</t>
+  </si>
+  <si>
+    <t>3231736314 3231736314</t>
+  </si>
+  <si>
+    <t>3231877276 3231877276</t>
+  </si>
+  <si>
+    <t>3231936669 3231936669</t>
+  </si>
+  <si>
+    <t>3232288506 3232288506</t>
+  </si>
+  <si>
+    <t>3232421005 3232421005</t>
+  </si>
+  <si>
+    <t>3232534489 3232534489</t>
   </si>
   <si>
     <t>Общи литри по продукт / КОМЕРС НОВИ ПАЗАР ЕООД</t>
@@ -515,24 +584,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -572,344 +643,541 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1186</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>79.81</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>114.93</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>121.31</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>23818</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1103</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>49.5</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
         <v>1.44</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>71.28</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>75.23999999999999</v>
       </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>242514</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1119</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
       </c>
       <c r="C4">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>4.6</v>
+        <v>63.22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="I4" s="1">
-        <v>4.6</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="J4">
-        <v>4.6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4">
+        <v>1.54</v>
+      </c>
+      <c r="K4" s="1">
+        <v>97.36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>113702</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1119</v>
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
       </c>
       <c r="C5">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>63.22</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.47</v>
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
       </c>
       <c r="H5">
-        <v>92.93000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="I5" s="1">
-        <v>1.54</v>
+        <v>4.6</v>
       </c>
       <c r="J5">
-        <v>97.36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5">
+        <v>4.6</v>
+      </c>
+      <c r="K5" s="1">
+        <v>4.6</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>113702</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1186</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
       </c>
       <c r="C6">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>75.8</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6">
         <v>1.48</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>112.18</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>116.73</v>
       </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>166017</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1103</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>78.01000000000001</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>116.23</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.54</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>120.14</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="L7">
+      <c r="C8">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>60.89</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8">
+        <v>1.5</v>
+      </c>
+      <c r="I8" s="1">
+        <v>91.34</v>
+      </c>
+      <c r="J8">
+        <v>1.56</v>
+      </c>
+      <c r="K8" s="1">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="M7">
-        <v>248109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3" t="s">
+      <c r="N8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9">
+        <v>45.56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>68.34</v>
+      </c>
+      <c r="J9">
+        <v>1.58</v>
+      </c>
+      <c r="K9" s="1">
+        <v>71.98</v>
+      </c>
+      <c r="L9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10">
+        <v>5.49</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5.49</v>
+      </c>
+      <c r="J10">
+        <v>5.49</v>
+      </c>
+      <c r="K10" s="1">
+        <v>5.49</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11">
+        <v>55.96</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11">
+        <v>1.5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>83.94</v>
+      </c>
+      <c r="J11">
+        <v>1.57</v>
+      </c>
+      <c r="K11" s="1">
+        <v>87.86</v>
+      </c>
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="6">
+        <v>508.75</v>
+      </c>
+      <c r="C16" s="6">
+        <v>8</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.4765</v>
+      </c>
+      <c r="E16" s="6">
+        <v>751.17</v>
+      </c>
+      <c r="F16" s="6">
+        <v>785.61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6">
-        <v>346.34</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.4655</v>
-      </c>
-      <c r="E12" s="6">
-        <v>507.55</v>
-      </c>
-      <c r="F12" s="6">
-        <v>530.78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="E13" s="6">
-        <v>4.6</v>
-      </c>
-      <c r="F13" s="6">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="9">
-        <v>347.34</v>
-      </c>
-      <c r="C14" s="9">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>512.15</v>
-      </c>
-      <c r="F14" s="9">
-        <v>535.38</v>
+      <c r="B17" s="6">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7">
+        <v>5.045</v>
+      </c>
+      <c r="E17" s="6">
+        <v>10.09</v>
+      </c>
+      <c r="F17" s="6">
+        <v>10.09</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="9">
+        <v>510.75</v>
+      </c>
+      <c r="C18" s="9">
+        <v>10</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="9">
+        <v>761.26</v>
+      </c>
+      <c r="F18" s="9">
+        <v>795.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
@@ -214,7 +214,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,12 +224,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,17 +273,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-05</t>
   </si>
   <si>
@@ -67,19 +76,19 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Асеновград</t>
-  </si>
-  <si>
-    <t>София Ботевградско шосе</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>Търговище</t>
+    <t>1119 Асеновград</t>
+  </si>
+  <si>
+    <t>1163 София Ботевградско шосе</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
   </si>
   <si>
     <t>78970110027720134</t>
@@ -88,22 +97,43 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-05 15:24:13</t>
-  </si>
-  <si>
-    <t>2026-06-11 10:16:50</t>
-  </si>
-  <si>
-    <t>2026-06-12 17:22:38</t>
-  </si>
-  <si>
-    <t>2026-06-17 09:38:49</t>
-  </si>
-  <si>
-    <t>2026-06-19 11:24:38</t>
-  </si>
-  <si>
-    <t>2026-06-25 13:31:54</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:29:00</t>
+  </si>
+  <si>
+    <t>10:16:00</t>
+  </si>
+  <si>
+    <t>17:23:00</t>
+  </si>
+  <si>
+    <t>09:37:00</t>
+  </si>
+  <si>
+    <t>11:24:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>3232912635 3232912635</t>
+  </si>
+  <si>
+    <t>3233190353 3233190353</t>
+  </si>
+  <si>
+    <t>3233261235 3233261235</t>
+  </si>
+  <si>
+    <t>3233476933 3233476933</t>
+  </si>
+  <si>
+    <t>3233587028 3233587028</t>
+  </si>
+  <si>
+    <t>3233855007 3233855007</t>
   </si>
   <si>
     <t>Общи литри по продукт / КОМЕРС НОВИ ПАЗАР ЕООД</t>
@@ -521,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,14 +560,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -571,220 +604,283 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>84.62</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
         <v>1.51</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>127.78</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>132.85</v>
       </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>61.84</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
         <v>1.48</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>91.52</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>96.47</v>
       </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>82.06</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4">
         <v>1.48</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>121.45</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.56</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>128.01</v>
       </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>53.51</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
         <v>1.46</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>78.12</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.56</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>83.48</v>
       </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>76.22</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6">
         <v>1.46</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>111.28</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>117.38</v>
       </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>75.26000000000001</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7">
         <v>1.42</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>106.87</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.52</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>114.4</v>
       </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -792,29 +888,29 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="6">
         <v>433.51</v>
@@ -832,9 +928,9 @@
         <v>672.59</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:14">
       <c r="A13" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B13" s="9">
         <v>433.51</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="63">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-08</t>
   </si>
   <si>
@@ -61,16 +67,43 @@
     <t>2026-07-12</t>
   </si>
   <si>
-    <t>София Ботевградско шосе</t>
-  </si>
-  <si>
-    <t>Русе Дружба</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Ихтиман</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1163 София Ботевградско шосе</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1186 Севлиево</t>
   </si>
   <si>
     <t>78970110027720134</t>
@@ -79,25 +112,79 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
-  </si>
-  <si>
-    <t>2026-07-08 06:33:34</t>
-  </si>
-  <si>
-    <t>2026-07-08 13:56:48</t>
-  </si>
-  <si>
-    <t>2026-07-09 08:16:02</t>
-  </si>
-  <si>
-    <t>2026-07-09 19:02:45</t>
-  </si>
-  <si>
-    <t>2026-07-09 19:02:46</t>
-  </si>
-  <si>
-    <t>2026-07-12 10:54:20</t>
+    <t>2L SUMMER SCREEN WASH LIQUID</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>06:33:00</t>
+  </si>
+  <si>
+    <t>13:56:00</t>
+  </si>
+  <si>
+    <t>08:17:00</t>
+  </si>
+  <si>
+    <t>19:04:00</t>
+  </si>
+  <si>
+    <t>10:53:00</t>
+  </si>
+  <si>
+    <t>07:40:00</t>
+  </si>
+  <si>
+    <t>15:40:00</t>
+  </si>
+  <si>
+    <t>17:25:00</t>
+  </si>
+  <si>
+    <t>17:20:00</t>
+  </si>
+  <si>
+    <t>10:29:00</t>
+  </si>
+  <si>
+    <t>14:26:00</t>
+  </si>
+  <si>
+    <t>3234465868 3234465868</t>
+  </si>
+  <si>
+    <t>3234480807 3234480807</t>
+  </si>
+  <si>
+    <t>3234497949 3234497949</t>
+  </si>
+  <si>
+    <t>3234553268 3234553268</t>
+  </si>
+  <si>
+    <t>3234682071 3234682071</t>
+  </si>
+  <si>
+    <t>3234875754 3234875754</t>
+  </si>
+  <si>
+    <t>3234948262 3234948262</t>
+  </si>
+  <si>
+    <t>3235193724 3235193724</t>
+  </si>
+  <si>
+    <t>3235376070 3235376070</t>
+  </si>
+  <si>
+    <t>3235518361 3235518361</t>
+  </si>
+  <si>
+    <t>3235595052 3235595052</t>
   </si>
   <si>
     <t>Общи литри по продукт / КОМЕРС НОВИ ПАЗАР ЕООД</t>
@@ -515,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -524,15 +611,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -569,180 +658,210 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>82.02</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2">
         <v>1.4</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>114.83</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.49</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>122.21</v>
       </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>40.59</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3">
         <v>1.4</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>56.83</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.49</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>60.48</v>
       </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>45</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4">
         <v>1.4</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>63</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.48</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>66.59999999999999</v>
       </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>55.03</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5">
         <v>1.4</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>77.04000000000001</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.48</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>81.44</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
         <v>25</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
       </c>
       <c r="C6">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
-        <v>4.99</v>
+      <c r="G6" t="s">
+        <v>34</v>
       </c>
       <c r="H6">
         <v>4.99</v>
@@ -753,142 +872,418 @@
       <c r="J6">
         <v>4.99</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>35.99</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7">
         <v>1.4</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>50.39</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.51</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>54.34</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>74.67</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8">
+        <v>1.41</v>
+      </c>
+      <c r="I8" s="1">
+        <v>105.28</v>
+      </c>
+      <c r="J8">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>112</v>
+      </c>
+      <c r="L8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>72.84</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9">
+        <v>1.41</v>
+      </c>
+      <c r="I9" s="1">
+        <v>102.7</v>
+      </c>
+      <c r="J9">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>109.26</v>
+      </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="L7">
+      <c r="C10">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10">
+        <v>1.44</v>
+      </c>
+      <c r="I10" s="1">
+        <v>101.87</v>
+      </c>
+      <c r="J10">
+        <v>1.56</v>
+      </c>
+      <c r="K10" s="1">
+        <v>110.35</v>
+      </c>
+      <c r="L10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3" t="s">
+      <c r="N10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="4" t="s">
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11">
+        <v>46.72</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11">
+        <v>1.44</v>
+      </c>
+      <c r="I11" s="1">
+        <v>67.28</v>
+      </c>
+      <c r="J11">
+        <v>1.59</v>
+      </c>
+      <c r="K11" s="1">
+        <v>74.28</v>
+      </c>
+      <c r="L11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12">
+        <v>63.89</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12">
+        <v>1.49</v>
+      </c>
+      <c r="I12" s="1">
+        <v>95.2</v>
+      </c>
+      <c r="J12">
+        <v>1.55</v>
+      </c>
+      <c r="K12" s="1">
+        <v>99.03</v>
+      </c>
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="E13" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="F13">
+        <v>81.02</v>
+      </c>
+      <c r="G13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13">
+        <v>1.49</v>
+      </c>
+      <c r="I13" s="1">
+        <v>120.72</v>
+      </c>
+      <c r="J13">
+        <v>1.55</v>
+      </c>
+      <c r="K13" s="1">
+        <v>125.58</v>
+      </c>
+      <c r="L13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="6">
+        <v>668.51</v>
+      </c>
+      <c r="C18" s="6">
+        <v>11</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1.4288</v>
+      </c>
+      <c r="E18" s="6">
+        <v>955.14</v>
+      </c>
+      <c r="F18" s="6">
+        <v>1015.57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="6">
-        <v>258.63</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="E12" s="6">
-        <v>362.09</v>
-      </c>
-      <c r="F12" s="6">
-        <v>385.07</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="6">
+      <c r="B19" s="6">
         <v>1</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C19" s="6">
         <v>1</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D19" s="7">
         <v>4.99</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E19" s="6">
         <v>4.99</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F19" s="6">
         <v>4.99</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="9">
-        <v>259.63</v>
-      </c>
-      <c r="C14" s="9">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>367.08</v>
-      </c>
-      <c r="F14" s="9">
-        <v>390.06</v>
+    <row r="20" spans="1:6">
+      <c r="A20" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="9">
+        <v>669.51</v>
+      </c>
+      <c r="C20" s="9">
+        <v>12</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="9">
+        <v>960.13</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1020.56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
@@ -211,7 +211,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1234,7 +1234,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="7">
-        <v>1.4288</v>
+        <v>1.428759</v>
       </c>
       <c r="E18" s="6">
         <v>955.14</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="64">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -602,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -615,13 +618,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -664,204 +667,219 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>82.02</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I2" s="1">
-        <v>114.83</v>
+        <v>1.399</v>
       </c>
       <c r="J2">
+        <v>114.74598</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.49</v>
       </c>
-      <c r="K2" s="1">
-        <v>122.21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>122.2098</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>40.59</v>
+        <v>40.591</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I3" s="1">
-        <v>56.83</v>
+        <v>1.399</v>
       </c>
       <c r="J3">
+        <v>56.786809</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.49</v>
       </c>
-      <c r="K3" s="1">
-        <v>60.48</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>60.48059</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I4" s="1">
-        <v>63</v>
+        <v>1.399</v>
       </c>
       <c r="J4">
+        <v>62.955</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.48</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>66.59999999999999</v>
       </c>
-      <c r="L4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>55.03</v>
+        <v>55.027</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I5" s="1">
-        <v>77.04000000000001</v>
+        <v>1.399</v>
       </c>
       <c r="J5">
+        <v>76.98277299999999</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.48</v>
       </c>
-      <c r="K5" s="1">
-        <v>81.44</v>
-      </c>
-      <c r="L5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>81.43996</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6">
         <v>4.99</v>
@@ -875,327 +893,351 @@
       <c r="K6" s="1">
         <v>4.99</v>
       </c>
-      <c r="L6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>35.99</v>
+        <v>35.987</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I7" s="1">
-        <v>50.39</v>
+        <v>1.399</v>
       </c>
       <c r="J7">
+        <v>50.345813</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.51</v>
       </c>
-      <c r="K7" s="1">
-        <v>54.34</v>
-      </c>
-      <c r="L7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>54.34037</v>
+      </c>
+      <c r="M7" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>74.67</v>
+        <v>74.673</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>1.41</v>
+        <v>1.369</v>
       </c>
       <c r="I8" s="1">
-        <v>105.28</v>
+        <v>1.409</v>
       </c>
       <c r="J8">
+        <v>105.214257</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.5</v>
       </c>
-      <c r="K8" s="1">
-        <v>112</v>
-      </c>
-      <c r="L8" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>112.0095</v>
+      </c>
+      <c r="M8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>72.84</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>1.41</v>
+        <v>1.369</v>
       </c>
       <c r="I9" s="1">
-        <v>102.7</v>
+        <v>1.409</v>
       </c>
       <c r="J9">
+        <v>102.63156</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>109.26</v>
       </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>70.73999999999999</v>
+        <v>70.73699999999999</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H10">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I10" s="1">
-        <v>101.87</v>
+        <v>1.441</v>
       </c>
       <c r="J10">
+        <v>101.932017</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.56</v>
       </c>
-      <c r="K10" s="1">
-        <v>110.35</v>
-      </c>
-      <c r="L10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>110.34972</v>
+      </c>
+      <c r="M10" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>46.72</v>
+        <v>46.717</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I11" s="1">
-        <v>67.28</v>
+        <v>1.441</v>
       </c>
       <c r="J11">
+        <v>67.319197</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.59</v>
       </c>
-      <c r="K11" s="1">
-        <v>74.28</v>
-      </c>
-      <c r="L11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>74.28003</v>
+      </c>
+      <c r="M11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12">
         <v>63.89</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I12" s="1">
-        <v>95.2</v>
+        <v>1.489</v>
       </c>
       <c r="J12">
+        <v>95.13221</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.55</v>
       </c>
-      <c r="K12" s="1">
-        <v>99.03</v>
-      </c>
-      <c r="L12" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12">
+      <c r="L12" s="1">
+        <v>99.0295</v>
+      </c>
+      <c r="M12" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>81.02</v>
+        <v>81.01900000000001</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H13">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I13" s="1">
-        <v>120.72</v>
+        <v>1.489</v>
       </c>
       <c r="J13">
+        <v>120.637291</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.55</v>
       </c>
-      <c r="K13" s="1">
-        <v>125.58</v>
-      </c>
-      <c r="L13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>125.57945</v>
+      </c>
+      <c r="M13" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1205,47 +1247,47 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" s="6">
-        <v>668.51</v>
+        <v>668.501</v>
       </c>
       <c r="C18" s="6">
         <v>11</v>
       </c>
       <c r="D18" s="7">
-        <v>1.428759</v>
+        <v>1.428095</v>
       </c>
       <c r="E18" s="6">
-        <v>955.14</v>
+        <v>954.6799999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>1015.57</v>
+        <v>1015.58</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6">
         <v>1</v>
@@ -1265,20 +1307,20 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="9">
-        <v>669.51</v>
+        <v>669.501</v>
       </c>
       <c r="C20" s="9">
         <v>12</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="9">
-        <v>960.13</v>
+        <v>959.67</v>
       </c>
       <c r="F20" s="9">
-        <v>1020.56</v>
+        <v>1020.57</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КОМЕРС НОВИ ПАЗАР ЕООД/КОМЕРС НОВИ ПАЗАР ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="63">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -213,8 +210,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -307,10 +304,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -605,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -618,13 +615,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -667,219 +664,204 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>13</v>
       </c>
       <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
         <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
       </c>
       <c r="F2">
         <v>82.02</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>1.399</v>
+        <v>114.746</v>
       </c>
       <c r="J2">
-        <v>114.74598</v>
+        <v>1.49</v>
       </c>
       <c r="K2" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L2" s="1">
-        <v>122.2098</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2">
+        <v>122.21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
       <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
         <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
       </c>
       <c r="F3">
         <v>40.591</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>1.399</v>
+        <v>56.787</v>
       </c>
       <c r="J3">
-        <v>56.786809</v>
+        <v>1.49</v>
       </c>
       <c r="K3" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L3" s="1">
-        <v>60.48059</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3">
+        <v>60.481</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>13</v>
       </c>
       <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
       </c>
       <c r="F4">
         <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H4">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I4" s="1">
-        <v>1.399</v>
+        <v>62.955</v>
       </c>
       <c r="J4">
-        <v>62.955</v>
+        <v>1.48</v>
       </c>
       <c r="K4" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="L4" s="1">
         <v>66.59999999999999</v>
       </c>
-      <c r="M4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
       </c>
       <c r="F5">
         <v>55.027</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H5">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I5" s="1">
-        <v>1.399</v>
+        <v>76.983</v>
       </c>
       <c r="J5">
-        <v>76.98277299999999</v>
+        <v>1.48</v>
       </c>
       <c r="K5" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="L5" s="1">
-        <v>81.43996</v>
-      </c>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5">
+        <v>81.44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H6">
         <v>4.99</v>
@@ -893,351 +875,327 @@
       <c r="K6" s="1">
         <v>4.99</v>
       </c>
-      <c r="L6" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6">
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
       <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
       </c>
       <c r="F7">
         <v>35.987</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I7" s="1">
-        <v>1.399</v>
+        <v>50.346</v>
       </c>
       <c r="J7">
-        <v>50.345813</v>
+        <v>1.51</v>
       </c>
       <c r="K7" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L7" s="1">
-        <v>54.34037</v>
-      </c>
-      <c r="M7" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7">
+        <v>54.34</v>
+      </c>
+      <c r="L7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
         <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
       </c>
       <c r="F8">
         <v>74.673</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H8">
-        <v>1.369</v>
+        <v>1.409</v>
       </c>
       <c r="I8" s="1">
-        <v>1.409</v>
+        <v>105.214</v>
       </c>
       <c r="J8">
-        <v>105.214257</v>
+        <v>1.5</v>
       </c>
       <c r="K8" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L8" s="1">
-        <v>112.0095</v>
-      </c>
-      <c r="M8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8">
+        <v>112.01</v>
+      </c>
+      <c r="L8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>13</v>
       </c>
       <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
         <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
       </c>
       <c r="F9">
         <v>72.84</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>1.369</v>
+        <v>1.409</v>
       </c>
       <c r="I9" s="1">
-        <v>1.409</v>
+        <v>102.632</v>
       </c>
       <c r="J9">
-        <v>102.63156</v>
+        <v>1.5</v>
       </c>
       <c r="K9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L9" s="1">
         <v>109.26</v>
       </c>
-      <c r="M9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>13</v>
       </c>
       <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
       </c>
       <c r="F10">
         <v>70.73699999999999</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I10" s="1">
-        <v>1.441</v>
+        <v>101.932</v>
       </c>
       <c r="J10">
-        <v>101.932017</v>
+        <v>1.56</v>
       </c>
       <c r="K10" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L10" s="1">
-        <v>110.34972</v>
-      </c>
-      <c r="M10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10">
+        <v>110.35</v>
+      </c>
+      <c r="L10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11">
         <v>13</v>
       </c>
       <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
         <v>31</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
       </c>
       <c r="F11">
         <v>46.717</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H11">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I11" s="1">
-        <v>1.441</v>
+        <v>67.319</v>
       </c>
       <c r="J11">
-        <v>67.319197</v>
+        <v>1.59</v>
       </c>
       <c r="K11" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="L11" s="1">
-        <v>74.28003</v>
-      </c>
-      <c r="M11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N11">
+        <v>74.28</v>
+      </c>
+      <c r="L11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>13</v>
       </c>
       <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
         <v>31</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
       </c>
       <c r="F12">
         <v>63.89</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H12">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I12" s="1">
-        <v>1.489</v>
+        <v>95.13200000000001</v>
       </c>
       <c r="J12">
-        <v>95.13221</v>
+        <v>1.55</v>
       </c>
       <c r="K12" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L12" s="1">
-        <v>99.0295</v>
-      </c>
-      <c r="M12" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12">
+        <v>99.03</v>
+      </c>
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>13</v>
       </c>
       <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
         <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
       </c>
       <c r="F13">
         <v>81.01900000000001</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H13">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I13" s="1">
-        <v>1.489</v>
+        <v>120.637</v>
       </c>
       <c r="J13">
-        <v>120.637291</v>
+        <v>1.55</v>
       </c>
       <c r="K13" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L13" s="1">
-        <v>125.57945</v>
-      </c>
-      <c r="M13" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13">
+        <v>125.579</v>
+      </c>
+      <c r="L13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-      <c r="O13" t="s">
+      <c r="N13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1247,67 +1205,67 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="6">
         <v>668.501</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <v>11</v>
       </c>
       <c r="D18" s="7">
-        <v>1.428095</v>
-      </c>
-      <c r="E18" s="6">
-        <v>954.6799999999999</v>
-      </c>
-      <c r="F18" s="6">
+        <v>1.428</v>
+      </c>
+      <c r="E18" s="7">
+        <v>954.683</v>
+      </c>
+      <c r="F18" s="7">
         <v>1015.58</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="6">
         <v>1</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
         <v>1</v>
       </c>
       <c r="D19" s="7">
         <v>4.99</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <v>4.99</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="7">
         <v>4.99</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="9">
         <v>669.501</v>
@@ -1317,7 +1275,7 @@
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="9">
-        <v>959.67</v>
+        <v>959.673</v>
       </c>
       <c r="F20" s="9">
         <v>1020.57</v>
